--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487865_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487865_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.6343</v>
+        <v>9.800700000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4374</v>
+        <v>2.925</v>
       </c>
       <c r="F2" t="n">
-        <v>8.196899999999999</v>
+        <v>6.8757</v>
       </c>
       <c r="G2" t="n">
         <v>8.138299999999999</v>
@@ -610,13 +610,13 @@
         <v>2.2893</v>
       </c>
       <c r="S2" t="n">
-        <v>4.2016</v>
+        <v>2.368</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0588</v>
+        <v>0.5463</v>
       </c>
       <c r="U2" t="n">
-        <v>3.1428</v>
+        <v>1.8216</v>
       </c>
       <c r="V2" t="n">
         <v>1.1675</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.4329</v>
+        <v>7.021</v>
       </c>
       <c r="E3" t="n">
-        <v>2.337</v>
+        <v>1.8665</v>
       </c>
       <c r="F3" t="n">
-        <v>5.0958</v>
+        <v>5.1545</v>
       </c>
       <c r="G3" t="n">
         <v>2.1263</v>
@@ -688,13 +688,13 @@
         <v>2.0812</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7041</v>
+        <v>1.2923</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4501</v>
+        <v>-0.0204</v>
       </c>
       <c r="U3" t="n">
-        <v>1.254</v>
+        <v>1.3127</v>
       </c>
       <c r="V3" t="n">
         <v>1.5213</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9666</v>
+        <v>3.3614</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7372</v>
+        <v>-0.6067</v>
       </c>
       <c r="F4" t="n">
-        <v>3.7038</v>
+        <v>3.968</v>
       </c>
       <c r="G4" t="n">
         <v>3.1065</v>
@@ -766,13 +766,13 @@
         <v>2.0812</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1109</v>
+        <v>0.5056</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.109</v>
+        <v>0.0215</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2199</v>
+        <v>0.4842</v>
       </c>
       <c r="V4" t="n">
         <v>-1.2914</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. TEIXEIRA DO VALE DIAS</t>
+          <t>L. GARCIA MUÑOZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6744</v>
+        <v>2.4466</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7139</v>
+        <v>0.5224</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3883</v>
+        <v>1.9242</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8116</v>
+        <v>2.8651</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3071</v>
+        <v>0.237</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4956</v>
+        <v>2.6281</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1231</v>
+        <v>1.4243</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2664</v>
+        <v>-0.273</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.3896</v>
+        <v>1.6973</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9347</v>
+        <v>1.4408</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0407</v>
+        <v>0.5101</v>
       </c>
       <c r="O5" t="n">
-        <v>0.894</v>
+        <v>0.9307</v>
       </c>
       <c r="P5" t="n">
+        <v>-1.0406</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-3.1218</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.0812</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.6221</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.1152</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.7373</v>
+      </c>
+      <c r="V5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-1.0406</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.0406</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-0.3047</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-0.7177</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.413</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.1675</v>
-      </c>
       <c r="W5" t="n">
-        <v>1.1675</v>
+        <v>2.3351</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. GARCIA MUÑOZ</t>
+          <t>T. TEIXEIRA DO VALE DIAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2327</v>
+        <v>2.2564</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2511</v>
+        <v>-0.22</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4838</v>
+        <v>2.4764</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8651</v>
+        <v>0.8116</v>
       </c>
       <c r="H6" t="n">
-        <v>0.237</v>
+        <v>1.3071</v>
       </c>
       <c r="I6" t="n">
-        <v>2.6281</v>
+        <v>-0.4956</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4243</v>
+        <v>-0.1231</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.273</v>
+        <v>1.2664</v>
       </c>
       <c r="L6" t="n">
-        <v>1.6973</v>
+        <v>-1.3896</v>
       </c>
       <c r="M6" t="n">
-        <v>1.4408</v>
+        <v>0.9347</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5101</v>
+        <v>0.0407</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9307</v>
+        <v>0.894</v>
       </c>
       <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>-1.0406</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-3.1218</v>
-      </c>
       <c r="R6" t="n">
-        <v>2.0812</v>
+        <v>1.0406</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5917</v>
+        <v>0.2773</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8885999999999999</v>
+        <v>-0.2238</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2969</v>
+        <v>0.5011</v>
       </c>
       <c r="V6" t="n">
+        <v>1.1675</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.1675</v>
+      </c>
+      <c r="X6" t="n">
         <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.3351</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-2.3351</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8666</v>
+        <v>1.2548</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5089</v>
+        <v>0.5741000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3577</v>
+        <v>0.6807</v>
       </c>
       <c r="G7" t="n">
         <v>1.7873</v>
@@ -1000,13 +1000,13 @@
         <v>0.6244</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3301</v>
+        <v>0.7183</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1272</v>
+        <v>0.1924</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2029</v>
+        <v>0.5259</v>
       </c>
       <c r="V7" t="n">
         <v>-1.8751</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5667</v>
+        <v>0.6254</v>
       </c>
       <c r="E8" t="n">
         <v>0.2418</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3249</v>
+        <v>0.3836</v>
       </c>
       <c r="G8" t="n">
         <v>0.5928</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0261</v>
+        <v>0.0326</v>
       </c>
       <c r="T8" t="n">
         <v>-0.06519999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0391</v>
+        <v>0.0979</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2676</v>
+        <v>0.0244</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7728</v>
+        <v>-2.8986</v>
       </c>
       <c r="F9" t="n">
-        <v>3.0404</v>
+        <v>2.923</v>
       </c>
       <c r="G9" t="n">
         <v>0.9986</v>
@@ -1156,13 +1156,13 @@
         <v>2.2893</v>
       </c>
       <c r="S9" t="n">
-        <v>1.0152</v>
+        <v>0.772</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.109</v>
+        <v>-0.2347</v>
       </c>
       <c r="U9" t="n">
-        <v>1.1242</v>
+        <v>1.0067</v>
       </c>
       <c r="V9" t="n">
         <v>1.1675</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3819</v>
+        <v>-0.1009</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2229</v>
+        <v>-2.2648</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8409</v>
+        <v>2.1639</v>
       </c>
       <c r="G10" t="n">
         <v>-0.6242</v>
@@ -1234,13 +1234,13 @@
         <v>0.8325</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1996</v>
+        <v>0.4807</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0619</v>
+        <v>0.02</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1377</v>
+        <v>0.4606</v>
       </c>
       <c r="V10" t="n">
         <v>1.2914</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4406</v>
+        <v>-2.3982</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3866</v>
+        <v>-3.2561</v>
       </c>
       <c r="F11" t="n">
-        <v>0.946</v>
+        <v>0.8579</v>
       </c>
       <c r="G11" t="n">
         <v>-1.8045</v>
@@ -1312,13 +1312,13 @@
         <v>1.4568</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3451</v>
+        <v>0.3875</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0438</v>
+        <v>0.0867</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3889</v>
+        <v>0.3008</v>
       </c>
       <c r="V11" t="n">
         <v>-1.3975</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.6262</v>
+        <v>-3.1198</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.1754</v>
+        <v>-5.6396</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5491</v>
+        <v>2.5198</v>
       </c>
       <c r="G12" t="n">
         <v>-0.7711</v>
@@ -1390,13 +1390,13 @@
         <v>0.8325</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.212</v>
+        <v>0.2944</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6524</v>
+        <v>-0.1167</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4404</v>
+        <v>0.4111</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3538</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>20.19309999999999</v>
+        <v>21.1718</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.7348</v>
+        <v>-8.756</v>
       </c>
       <c r="F13" t="n">
-        <v>29.9276</v>
+        <v>29.9277</v>
       </c>
       <c r="G13" t="n">
         <v>17.2267</v>
@@ -1444,7 +1444,7 @@
         <v>5.3489</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.8557999999999999</v>
+        <v>-0.8558000000000003</v>
       </c>
       <c r="L13" t="n">
         <v>6.2046</v>
@@ -1468,13 +1468,13 @@
         <v>15.609</v>
       </c>
       <c r="S13" t="n">
-        <v>6.7721</v>
+        <v>7.7508</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8877</v>
+        <v>0.09090000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>7.659800000000001</v>
+        <v>7.659900000000001</v>
       </c>
       <c r="V13" t="n">
         <v>1.3974</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7837</v>
+        <v>0.9266</v>
       </c>
       <c r="E14" t="n">
         <v>-0.1537</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9374</v>
+        <v>1.0803</v>
       </c>
       <c r="G14" t="n">
         <v>-0.9614</v>
@@ -1546,13 +1546,13 @@
         <v>1.6649</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8853</v>
+        <v>-0.7425</v>
       </c>
       <c r="T14" t="n">
         <v>-0.721</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1643</v>
+        <v>-0.0215</v>
       </c>
       <c r="V14" t="n">
         <v>2.006</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. DOMINGUEZ ESPELT</t>
+          <t>D. CEBOLLA PORCAR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.698</v>
+        <v>-0.1195</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.6446</v>
+        <v>-3.0241</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9465</v>
+        <v>2.9046</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.1036</v>
+        <v>-1.6425</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0725</v>
+        <v>-0.8702</v>
       </c>
       <c r="I15" t="n">
-        <v>-4.176</v>
+        <v>-0.7723</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.1564</v>
+        <v>-1.52</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4155</v>
+        <v>-1.3844</v>
       </c>
       <c r="L15" t="n">
-        <v>-3.5719</v>
+        <v>-0.1355</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9472</v>
+        <v>-0.1226</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3431</v>
+        <v>0.5142</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6041</v>
+        <v>-0.6368</v>
       </c>
       <c r="P15" t="n">
-        <v>1.4568</v>
+        <v>0.6244</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4568</v>
+        <v>2.7055</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9265</v>
+        <v>-0.2936</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6556999999999999</v>
+        <v>-0.5905</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2707</v>
+        <v>0.2969</v>
       </c>
       <c r="V15" t="n">
-        <v>1.8751</v>
+        <v>1.1923</v>
       </c>
       <c r="W15" t="n">
         <v>1.1675</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7076</v>
+        <v>0.0248</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. CEBOLLA PORCAR</t>
+          <t>A. DOMINGUEZ ESPELT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6988</v>
+        <v>-0.7362</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.0241</v>
+        <v>-1.8589</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3253</v>
+        <v>1.1227</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.6425</v>
+        <v>-3.1036</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8702</v>
+        <v>1.0725</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7723</v>
+        <v>-4.176</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.52</v>
+        <v>-2.1564</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.3844</v>
+        <v>1.4155</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.1355</v>
+        <v>-3.5719</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1226</v>
+        <v>-0.9472</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5142</v>
+        <v>-0.3431</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6368</v>
+        <v>-0.6041</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6244</v>
+        <v>1.4568</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7055</v>
+        <v>1.4568</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8729</v>
+        <v>-0.9646</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5905</v>
+        <v>-0.87</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2824</v>
+        <v>-0.0946</v>
       </c>
       <c r="V16" t="n">
-        <v>1.1923</v>
+        <v>1.8751</v>
       </c>
       <c r="W16" t="n">
         <v>1.1675</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0248</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1413</v>
+        <v>-0.9857</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.4257</v>
+        <v>-2.2114</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2844</v>
+        <v>1.2257</v>
       </c>
       <c r="G17" t="n">
         <v>-0.4471</v>
@@ -1780,13 +1780,13 @@
         <v>1.4568</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.5979</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0439</v>
+        <v>-0.8296</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2904</v>
+        <v>0.2317</v>
       </c>
       <c r="V17" t="n">
         <v>-1.3975</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>R. LLAMAS MARTINEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.6563</v>
+        <v>-1.2533</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.5132</v>
+        <v>-1.2027</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8569</v>
+        <v>-0.0506</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5225</v>
+        <v>-1.1487</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7911</v>
+        <v>0.774</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3136</v>
+        <v>-1.9227</v>
       </c>
       <c r="J18" t="n">
-        <v>1.58</v>
+        <v>0.4517</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3011</v>
+        <v>1.1661</v>
       </c>
       <c r="L18" t="n">
-        <v>1.881</v>
+        <v>-0.7144</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0575</v>
+        <v>-1.6004</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4901</v>
+        <v>-0.3921</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5674</v>
+        <v>-1.2083</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.4162</v>
+        <v>1.4568</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.1218</v>
+        <v>-1.0406</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7055</v>
+        <v>2.4974</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1174</v>
+        <v>-0.4187</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7862</v>
+        <v>-0.6138</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6688</v>
+        <v>0.1951</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.6452</v>
+        <v>-1.1428</v>
       </c>
       <c r="W18" t="n">
-        <v>-1.1852</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.4599</v>
+        <v>-1.1428</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. LLAMAS MARTINEZ</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6756</v>
+        <v>-1.9039</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3099</v>
+        <v>-3.7276</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3657</v>
+        <v>1.8236</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1487</v>
+        <v>0.5225</v>
       </c>
       <c r="H19" t="n">
-        <v>0.774</v>
+        <v>-0.7911</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.9227</v>
+        <v>1.3136</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4517</v>
+        <v>1.58</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1661</v>
+        <v>-0.3011</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7144</v>
+        <v>1.881</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6004</v>
+        <v>-1.0575</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3921</v>
+        <v>-0.4901</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2083</v>
+        <v>-0.5674</v>
       </c>
       <c r="P19" t="n">
-        <v>1.4568</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="R19" t="n">
-        <v>2.4974</v>
+        <v>2.7055</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.841</v>
+        <v>-0.365</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.721</v>
+        <v>-1.0005</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.12</v>
+        <v>0.6355</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.1428</v>
+        <v>-1.6452</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-1.1852</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.1428</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4912</v>
+        <v>-2.3561</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.8419</v>
+        <v>-4.4132</v>
       </c>
       <c r="F20" t="n">
-        <v>2.3507</v>
+        <v>2.0571</v>
       </c>
       <c r="G20" t="n">
         <v>-3.8478</v>
@@ -2014,13 +2014,13 @@
         <v>1.4568</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4164</v>
+        <v>-1.2813</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.6311</v>
+        <v>-1.2025</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2147</v>
+        <v>-0.0789</v>
       </c>
       <c r="V20" t="n">
         <v>1.3161</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9897</v>
+        <v>-2.6286</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.462</v>
+        <v>-2.2477</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5276999999999999</v>
+        <v>-0.3809</v>
       </c>
       <c r="G21" t="n">
         <v>-0.3829</v>
@@ -2092,13 +2092,13 @@
         <v>1.4568</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9179</v>
+        <v>-0.5568</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9134</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0045</v>
+        <v>0.1423</v>
       </c>
       <c r="V21" t="n">
         <v>-2.1051</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7419</v>
+        <v>-2.7046</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2049</v>
+        <v>-2.7763</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5371</v>
+        <v>0.0716</v>
       </c>
       <c r="G22" t="n">
         <v>0.6304</v>
@@ -2170,13 +2170,13 @@
         <v>2.4974</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.543</v>
+        <v>-0.5056</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2396</v>
+        <v>-0.8110000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3033</v>
+        <v>0.3054</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1238</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.8839</v>
+        <v>-7.0029</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.3478</v>
+        <v>-8.312200000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>1.4639</v>
+        <v>1.3093</v>
       </c>
       <c r="G23" t="n">
         <v>-6.8455</v>
@@ -2248,13 +2248,13 @@
         <v>2.9137</v>
       </c>
       <c r="S23" t="n">
-        <v>1.5018</v>
+        <v>0.3828</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6425</v>
+        <v>-0.3219</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8593</v>
+        <v>0.7047</v>
       </c>
       <c r="V23" t="n">
         <v>-1.3727</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-20.193</v>
+        <v>-18.7642</v>
       </c>
       <c r="E24" t="n">
         <v>-29.9278</v>
       </c>
       <c r="F24" t="n">
-        <v>9.7346</v>
+        <v>11.1634</v>
       </c>
       <c r="G24" t="n">
         <v>-17.2266</v>
@@ -2326,16 +2326,16 @@
         <v>20.8116</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.772099999999999</v>
+        <v>-5.343200000000001</v>
       </c>
       <c r="T24" t="n">
         <v>-7.6599</v>
       </c>
       <c r="U24" t="n">
-        <v>0.8879999999999999</v>
+        <v>2.3166</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.3976</v>
+        <v>-1.397600000000001</v>
       </c>
       <c r="W24" t="n">
         <v>5.2186</v>
